--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-08).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-08).xlsx
@@ -935,19 +935,19 @@
     <t>214</t>
   </si>
   <si>
-    <t>23</t>
+    <t>19</t>
   </si>
   <si>
-    <t>R$ 4.578,45</t>
+    <t>R$ 4.547,92</t>
   </si>
   <si>
-    <t>49.4</t>
+    <t>49.0</t>
   </si>
   <si>
-    <t>28.5</t>
+    <t>28.4</t>
   </si>
   <si>
-    <t>5.40</t>
+    <t>5.37</t>
   </si>
   <si>
     <t>19.2</t>
@@ -956,10 +956,10 @@
     <t>7.2</t>
   </si>
   <si>
-    <t>6.3</t>
+    <t>6.4</t>
   </si>
   <si>
-    <t>41.9%</t>
+    <t>42.3%</t>
   </si>
   <si>
     <t>17.1%</t>
@@ -989,13 +989,13 @@
     <t>3.4%</t>
   </si>
   <si>
-    <t>1157.0</t>
+    <t>1158.0</t>
   </si>
   <si>
-    <t>917.0</t>
+    <t>918.0</t>
   </si>
   <si>
-    <t>99.0</t>
+    <t>100.0</t>
   </si>
   <si>
     <t>34.0</t>
@@ -5019,7 +5019,7 @@
         <v>19536</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C24" s="4">
         <v>51</v>
@@ -5049,14 +5049,26 @@
         <v>58</v>
       </c>
       <c r="L24" s="4"/>
-      <c r="M24" s="5"/>
-      <c r="N24" s="6"/>
+      <c r="M24" s="5">
+        <v>4031</v>
+      </c>
+      <c r="N24" s="6">
+        <v>43</v>
+      </c>
       <c r="O24" s="6"/>
-      <c r="P24" s="7"/>
-      <c r="Q24" s="8"/>
-      <c r="R24" s="8"/>
+      <c r="P24" s="7">
+        <v>3.1562023255813956</v>
+      </c>
+      <c r="Q24" s="8">
+        <v>16.298959374999999</v>
+      </c>
+      <c r="R24" s="8">
+        <v>6.171875</v>
+      </c>
       <c r="S24" s="8"/>
-      <c r="T24" s="9"/>
+      <c r="T24" s="9">
+        <v>0.46875</v>
+      </c>
       <c r="U24" s="9"/>
       <c r="V24" s="9"/>
       <c r="W24" s="9"/>
@@ -6843,7 +6855,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>51</v>
@@ -6873,14 +6885,26 @@
         <v>58</v>
       </c>
       <c r="L36" s="4"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="6"/>
+      <c r="M36" s="5">
+        <v>3057.5500000000002</v>
+      </c>
+      <c r="N36" s="6">
+        <v>30</v>
+      </c>
       <c r="O36" s="6"/>
-      <c r="P36" s="7"/>
-      <c r="Q36" s="8"/>
-      <c r="R36" s="8"/>
+      <c r="P36" s="7">
+        <v>5.274443333333334</v>
+      </c>
+      <c r="Q36" s="8">
+        <v>15.059999999999999</v>
+      </c>
+      <c r="R36" s="8">
+        <v>3.0108350000000002</v>
+      </c>
       <c r="S36" s="8"/>
-      <c r="T36" s="9"/>
+      <c r="T36" s="9">
+        <v>0.40000000000000002</v>
+      </c>
       <c r="U36" s="9"/>
       <c r="V36" s="9"/>
       <c r="W36" s="9"/>
@@ -9132,7 +9156,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>51</v>
@@ -9162,14 +9186,26 @@
         <v>58</v>
       </c>
       <c r="L51" s="4"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="6"/>
+      <c r="M51" s="5">
+        <v>1234</v>
+      </c>
+      <c r="N51" s="6">
+        <v>9</v>
+      </c>
       <c r="O51" s="6"/>
-      <c r="P51" s="7"/>
-      <c r="Q51" s="8"/>
-      <c r="R51" s="8"/>
+      <c r="P51" s="7">
+        <v>4.957411111111111</v>
+      </c>
+      <c r="Q51" s="8">
+        <v>26.349999999999998</v>
+      </c>
+      <c r="R51" s="8">
+        <v>14.011899999999999</v>
+      </c>
       <c r="S51" s="8"/>
-      <c r="T51" s="9"/>
+      <c r="T51" s="9">
+        <v>0</v>
+      </c>
       <c r="U51" s="9"/>
       <c r="V51" s="9"/>
       <c r="W51" s="9"/>
@@ -14834,7 +14870,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>51</v>
@@ -14862,14 +14898,26 @@
         <v>58</v>
       </c>
       <c r="L89" s="4"/>
-      <c r="M89" s="5"/>
-      <c r="N89" s="6"/>
+      <c r="M89" s="5">
+        <v>4038.7800000000002</v>
+      </c>
+      <c r="N89" s="6">
+        <v>43</v>
+      </c>
       <c r="O89" s="6"/>
-      <c r="P89" s="7"/>
-      <c r="Q89" s="8"/>
-      <c r="R89" s="8"/>
+      <c r="P89" s="7">
+        <v>3.8601634146341461</v>
+      </c>
+      <c r="Q89" s="8">
+        <v>19.193592307692306</v>
+      </c>
+      <c r="R89" s="8">
+        <v>8.375</v>
+      </c>
       <c r="S89" s="8"/>
-      <c r="T89" s="9"/>
+      <c r="T89" s="9">
+        <v>0.61538461538461542</v>
+      </c>
       <c r="U89" s="9"/>
       <c r="V89" s="9"/>
       <c r="W89" s="9"/>
@@ -28444,7 +28492,9 @@
       <c r="N179" s="6">
         <v>52</v>
       </c>
-      <c r="O179" s="6"/>
+      <c r="O179" s="6">
+        <v>25</v>
+      </c>
       <c r="P179" s="7">
         <v>3.1540816326530616</v>
       </c>
@@ -28454,31 +28504,75 @@
       <c r="R179" s="8">
         <v>1.2566679999999999</v>
       </c>
-      <c r="S179" s="8"/>
+      <c r="S179" s="8">
+        <v>7</v>
+      </c>
       <c r="T179" s="9">
         <v>0.92000000000000004</v>
       </c>
-      <c r="U179" s="9"/>
-      <c r="V179" s="9"/>
-      <c r="W179" s="9"/>
-      <c r="X179" s="9"/>
-      <c r="Y179" s="9"/>
-      <c r="Z179" s="9"/>
-      <c r="AA179" s="9"/>
-      <c r="AB179" s="9"/>
-      <c r="AC179" s="9"/>
-      <c r="AD179" s="6"/>
-      <c r="AE179" s="6"/>
-      <c r="AF179" s="6"/>
-      <c r="AG179" s="6"/>
-      <c r="AH179" s="6"/>
-      <c r="AI179" s="6"/>
-      <c r="AJ179" s="6"/>
-      <c r="AK179" s="6"/>
-      <c r="AL179" s="6"/>
-      <c r="AM179" s="6"/>
-      <c r="AN179" s="9"/>
-      <c r="AO179" s="6"/>
+      <c r="U179" s="9">
+        <v>0.040000000000000001</v>
+      </c>
+      <c r="V179" s="9">
+        <v>0.040000000000000001</v>
+      </c>
+      <c r="W179" s="9">
+        <v>0</v>
+      </c>
+      <c r="X179" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y179" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD179" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE179" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF179" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO179" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP179" s="4">
         <v>58</v>
       </c>
